--- a/static/example_sheets/Field sampling (internal).xlsx
+++ b/static/example_sheets/Field sampling (internal).xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\glj523\Documents\github repoes\upload_web_app\static\example_sheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magnu\Documents\Git Repoes\gg-metadatabase-ui\static\example_sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D9F7BE7-A126-4D58-855A-DDAB1F6D4FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44CC760C-142B-42A8-8C5A-0BB8674B0DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{F20BE04D-14A6-4DFA-9322-DA461E992517}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{F20BE04D-14A6-4DFA-9322-DA461E992517}"/>
   </bookViews>
   <sheets>
     <sheet name="eDNA_Archive_sampling_(20231027" sheetId="2" r:id="rId1"/>
@@ -46,9 +46,9 @@
   <commentList>
     <comment ref="O1" authorId="0" shapeId="0" xr:uid="{6FC7414E-1184-43F7-9F14-90F3FC65C183}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t xml:space="preserve">[Trådet kommentar]
+Din version af Excel lader dig læse denne trådede kommentar. Eventuelle ændringer vil dog blive fjernet, hvis filen åbnes i en nyere version af Excel. Få mere at vide: https://go.microsoft.com/fwlink/?linkid=870924
+Kommentar:
     URI: MIXS:0000018 </t>
       </text>
     </comment>
@@ -118,9 +118,6 @@
     <t>Grant</t>
   </si>
   <si>
-    <t xml:space="preserve">Sampling site </t>
-  </si>
-  <si>
     <t>Sediment type</t>
   </si>
   <si>
@@ -148,15 +145,6 @@
     <t>Sample storage address</t>
   </si>
   <si>
-    <t xml:space="preserve">Sample storage location </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Storing date </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disposal date </t>
-  </si>
-  <si>
     <t>Link to images</t>
   </si>
   <si>
@@ -181,9 +169,6 @@
     <t>&lt;ku-id&gt;_&lt;sampling_site&gt;_&lt;sampling_date&gt;_&lt;no&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">Latitude </t>
-  </si>
-  <si>
     <t>Longitude</t>
   </si>
   <si>
@@ -196,9 +181,6 @@
     <t>Sampling depth (discrete, cm)</t>
   </si>
   <si>
-    <t xml:space="preserve">Sampling depth (interval, cm) </t>
-  </si>
-  <si>
     <t>Sample provider(s)</t>
   </si>
   <si>
@@ -211,9 +193,6 @@
     <t>Outcrop, cave, lake, bog etc.</t>
   </si>
   <si>
-    <t xml:space="preserve">Sampling depth reference </t>
-  </si>
-  <si>
     <t>Sample storage setting</t>
   </si>
   <si>
@@ -310,9 +289,6 @@
     <t>Specify as negative number if below mean sea level.</t>
   </si>
   <si>
-    <t>37.5</t>
-  </si>
-  <si>
     <t>Any relevant measurements/observations taken of the field sample. If multiple: seperate by semi-colon.</t>
   </si>
   <si>
@@ -376,9 +352,6 @@
     <t>Country/Ocean</t>
   </si>
   <si>
-    <t xml:space="preserve">Sampling Date </t>
-  </si>
-  <si>
     <t>Date when the sampling occured.</t>
   </si>
   <si>
@@ -428,6 +401,33 @@
   </si>
   <si>
     <t>[10, 20)</t>
+  </si>
+  <si>
+    <t>Latitude</t>
+  </si>
+  <si>
+    <t>Sampling depth (interval, cm)</t>
+  </si>
+  <si>
+    <t>Sampling depth reference</t>
+  </si>
+  <si>
+    <t>Sample storage location</t>
+  </si>
+  <si>
+    <t>Storing date</t>
+  </si>
+  <si>
+    <t>Disposal date</t>
+  </si>
+  <si>
+    <t>Sampling site</t>
+  </si>
+  <si>
+    <t>Sampling Date</t>
+  </si>
+  <si>
+    <t>37,5</t>
   </si>
 </sst>
 </file>
@@ -668,10 +668,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="8">
-    <cellStyle name="Check Cell" xfId="6" builtinId="23"/>
     <cellStyle name="Comma 2" xfId="3" xr:uid="{8942F21F-F0D4-468F-A2D9-2DD07A9F09D0}"/>
     <cellStyle name="Explanatory Text 2" xfId="2" xr:uid="{EEC8BC1F-FCCB-4C2D-96AE-E4673B111AFF}"/>
-    <cellStyle name="Hyperlink" xfId="7" builtinId="8"/>
+    <cellStyle name="Kontrollér celle" xfId="6" builtinId="23"/>
+    <cellStyle name="Link" xfId="7" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{C43A14CE-CD9A-4CDB-8396-19B2B1DC1FD5}"/>
     <cellStyle name="Normal 4" xfId="4" xr:uid="{1133FEEC-7998-4312-B355-8FD805FAFB7D}"/>
@@ -697,9 +697,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022 Tema">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -737,7 +737,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -843,7 +843,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -985,7 +985,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1067,31 +1067,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>118</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>15</v>
@@ -1100,73 +1100,73 @@
         <v>16</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="N1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="AE1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AG1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AA1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="AD1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:35" s="18" customFormat="1" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
@@ -1174,16 +1174,16 @@
         <v>9</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="G2" s="19">
         <v>61.139899999999997</v>
@@ -1192,28 +1192,28 @@
         <v>-45.534700000000001</v>
       </c>
       <c r="I2" s="18" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="J2" s="18" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="K2" s="18" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="L2" s="18" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="M2" s="18" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="N2" s="18">
         <v>10</v>
       </c>
       <c r="O2" s="18" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="P2" s="18" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="Q2" s="18">
         <v>10</v>
@@ -1225,58 +1225,58 @@
         <v>4</v>
       </c>
       <c r="T2" s="18" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="U2" s="19" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="V2" s="18" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="W2" s="18" t="s">
         <v>5</v>
       </c>
       <c r="X2" s="18" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="Y2" s="18">
         <v>37</v>
       </c>
       <c r="Z2" s="18" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="AA2" s="18" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AB2" s="18" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="AC2" s="18" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="AD2" s="18" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="AE2" s="18" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AF2" s="18" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:35" s="18" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="18" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="G3" s="19">
         <v>61.139899999999997</v>
@@ -1285,28 +1285,28 @@
         <v>-45.534700000000001</v>
       </c>
       <c r="I3" s="18" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="J3" s="18" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="K3" s="18" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="L3" s="18" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="M3" s="18" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="N3" s="18">
         <v>200</v>
       </c>
       <c r="O3" s="18" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="P3" s="18" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="Q3" s="18">
         <v>200</v>
@@ -1315,61 +1315,61 @@
         <v>200</v>
       </c>
       <c r="S3" s="18" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="T3" s="18" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="U3" s="19" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="V3" s="18" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="W3" s="18" t="s">
         <v>5</v>
       </c>
       <c r="X3" s="18" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="Y3" s="18">
         <v>37</v>
       </c>
       <c r="Z3" s="18" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="AA3" s="18" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="AB3" s="18" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="AC3" s="18" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="AD3" s="18" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="AE3" s="18" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AF3" s="18" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:35" s="18" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="18" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="G4" s="19">
         <v>61.139899999999997</v>
@@ -1378,76 +1378,76 @@
         <v>-45.534700000000001</v>
       </c>
       <c r="I4" s="18" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="J4" s="18" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="K4" s="18" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="L4" s="18" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="M4" s="18" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="N4" s="18" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="O4" s="18" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="P4" s="18" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="Q4" s="18" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="R4" s="18" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="S4" s="18" t="s">
         <v>6</v>
       </c>
       <c r="T4" s="18" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="U4" s="19" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="V4" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="W4" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="X4" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="Y4" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="Z4" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA4" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB4" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC4" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD4" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="AE4" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="W4" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="X4" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y4" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="Z4" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA4" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="AB4" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="AC4" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="AD4" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="AE4" s="18" t="s">
-        <v>84</v>
-      </c>
       <c r="AF4" s="18" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:35" s="6" customFormat="1" ht="81.599999999999994" x14ac:dyDescent="0.3">
@@ -1455,17 +1455,17 @@
         <v>2</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>7</v>
@@ -1474,85 +1474,85 @@
         <v>8</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="O6" s="20" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="S6" s="5" t="s">
         <v>11</v>
       </c>
       <c r="T6" s="5" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="U6" s="5" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="V6" s="5" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="W6" s="5" t="s">
         <v>13</v>
       </c>
       <c r="X6" s="20" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="Y6" s="5" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="Z6" s="5" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="AA6" s="5" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="AB6" s="5" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="AC6" s="5" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="AD6" s="5" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="AE6" s="5" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AF6" s="5" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AG6" s="5" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="AH6" s="5" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="AI6" s="5" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:35" s="5" customFormat="1" ht="61.2" x14ac:dyDescent="0.3">
@@ -1560,81 +1560,81 @@
         <v>12</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="G7" s="9" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H7" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="O7" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="P7" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q7" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="R7" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="S7" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K7" s="5" t="s">
+      <c r="U7" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="X7" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y7" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z7" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AB7" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AC7" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD7" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AE7" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="L7" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="N7" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="O7" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="P7" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q7" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="R7" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="S7" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="U7" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="X7" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y7" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z7" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB7" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="AC7" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="AD7" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="AE7" s="5" t="s">
-        <v>82</v>
-      </c>
       <c r="AF7" s="5" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AG7" s="5" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="AH7" s="5" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:35" s="6" customFormat="1" x14ac:dyDescent="0.3">

--- a/static/example_sheets/Field sampling (internal).xlsx
+++ b/static/example_sheets/Field sampling (internal).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magnu\Documents\Git Repoes\gg-metadatabase-ui\static\example_sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44CC760C-142B-42A8-8C5A-0BB8674B0DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24DB60C5-7750-4D8C-B0E8-2FB49C853E4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{F20BE04D-14A6-4DFA-9322-DA461E992517}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F20BE04D-14A6-4DFA-9322-DA461E992517}"/>
   </bookViews>
   <sheets>
     <sheet name="eDNA_Archive_sampling_(20231027" sheetId="2" r:id="rId1"/>

--- a/static/example_sheets/Field sampling (internal).xlsx
+++ b/static/example_sheets/Field sampling (internal).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magnu\Documents\Git Repoes\gg-metadatabase-ui\static\example_sheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Documents\GitHub repoes\gg-metadatabase-ui\static\example_sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24DB60C5-7750-4D8C-B0E8-2FB49C853E4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A048FC97-8BBA-4921-BA3B-9F99F29D3D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F20BE04D-14A6-4DFA-9322-DA461E992517}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F20BE04D-14A6-4DFA-9322-DA461E992517}"/>
   </bookViews>
   <sheets>
     <sheet name="eDNA_Archive_sampling_(20231027" sheetId="2" r:id="rId1"/>
@@ -385,9 +385,6 @@
     <t>text and/or numbers</t>
   </si>
   <si>
-    <t>300,3</t>
-  </si>
-  <si>
     <t>[1, 105)</t>
   </si>
   <si>
@@ -427,7 +424,10 @@
     <t>Sampling Date</t>
   </si>
   <si>
-    <t>37,5</t>
+    <t>300.3</t>
+  </si>
+  <si>
+    <t>37.5</t>
   </si>
 </sst>
 </file>
@@ -1008,61 +1008,61 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92B8DB45-AD95-4AEF-BE44-A884078F1D25}">
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.81640625" customWidth="1"/>
+    <col min="3" max="3" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="21.21875" customWidth="1"/>
-    <col min="9" max="9" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.1796875" customWidth="1"/>
+    <col min="9" max="9" width="13.1796875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="8.88671875" customWidth="1"/>
-    <col min="13" max="13" width="29.77734375" customWidth="1"/>
-    <col min="14" max="14" width="16.109375" customWidth="1"/>
-    <col min="15" max="15" width="18.21875" customWidth="1"/>
-    <col min="16" max="16" width="16.5546875" customWidth="1"/>
-    <col min="17" max="17" width="17.21875" customWidth="1"/>
-    <col min="18" max="18" width="16.5546875" customWidth="1"/>
-    <col min="19" max="19" width="17.6640625" customWidth="1"/>
-    <col min="20" max="20" width="14.5546875" customWidth="1"/>
-    <col min="21" max="21" width="11.109375" customWidth="1"/>
-    <col min="22" max="22" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.5546875" customWidth="1"/>
-    <col min="25" max="25" width="18.21875" customWidth="1"/>
-    <col min="26" max="26" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.90625" customWidth="1"/>
+    <col min="13" max="13" width="29.81640625" customWidth="1"/>
+    <col min="14" max="14" width="16.08984375" customWidth="1"/>
+    <col min="15" max="15" width="18.1796875" customWidth="1"/>
+    <col min="16" max="16" width="16.54296875" customWidth="1"/>
+    <col min="17" max="17" width="17.1796875" customWidth="1"/>
+    <col min="18" max="18" width="16.54296875" customWidth="1"/>
+    <col min="19" max="19" width="17.6328125" customWidth="1"/>
+    <col min="20" max="20" width="14.54296875" customWidth="1"/>
+    <col min="21" max="21" width="11.08984375" customWidth="1"/>
+    <col min="22" max="22" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.54296875" customWidth="1"/>
+    <col min="25" max="25" width="18.1796875" customWidth="1"/>
+    <col min="26" max="26" width="21.36328125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="20.36328125" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="25" customWidth="1"/>
-    <col min="29" max="29" width="12.6640625" customWidth="1"/>
-    <col min="30" max="30" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="31.5546875" customWidth="1"/>
-    <col min="32" max="32" width="43.6640625" customWidth="1"/>
-    <col min="33" max="33" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="18.44140625" customWidth="1"/>
-    <col min="36" max="36" width="56.44140625" customWidth="1"/>
-    <col min="37" max="37" width="33.21875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="48.109375" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.6328125" customWidth="1"/>
+    <col min="30" max="30" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="31.54296875" customWidth="1"/>
+    <col min="32" max="32" width="43.6328125" customWidth="1"/>
+    <col min="33" max="33" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="19.36328125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="18.453125" customWidth="1"/>
+    <col min="36" max="36" width="56.453125" customWidth="1"/>
+    <col min="37" max="37" width="33.1796875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="48.08984375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="26.6328125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="23.6328125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="9.36328125" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="22" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="26.6640625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="15.6640625" customWidth="1"/>
-    <col min="50" max="50" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="26.6328125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="23.6328125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="15.6328125" customWidth="1"/>
+    <col min="50" max="50" width="10.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" s="15" customFormat="1" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:35" s="15" customFormat="1" ht="59" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -1079,16 +1079,16 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>34</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>38</v>
@@ -1106,10 +1106,10 @@
         <v>37</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="Q1" s="3" t="s">
         <v>60</v>
@@ -1145,13 +1145,13 @@
         <v>42</v>
       </c>
       <c r="AB1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AC1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="AD1" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="AE1" s="1" t="s">
         <v>23</v>
@@ -1169,7 +1169,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:35" s="18" customFormat="1" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:35" s="18" customFormat="1" ht="16" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>10</v>
       </c>
       <c r="O2" s="18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P2" s="18" t="s">
         <v>43</v>
@@ -1237,7 +1237,7 @@
         <v>5</v>
       </c>
       <c r="X2" s="18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Y2" s="18">
         <v>37</v>
@@ -1264,7 +1264,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="3" spans="1:35" s="18" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:35" s="18" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="4"/>
       <c r="B3" s="18" t="s">
         <v>31</v>
@@ -1303,7 +1303,7 @@
         <v>200</v>
       </c>
       <c r="O3" s="18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P3" s="18" t="s">
         <v>44</v>
@@ -1330,7 +1330,7 @@
         <v>5</v>
       </c>
       <c r="X3" s="18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Y3" s="18">
         <v>37</v>
@@ -1357,7 +1357,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:35" s="18" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:35" s="18" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="4"/>
       <c r="B4" s="18" t="s">
         <v>32</v>
@@ -1393,19 +1393,19 @@
         <v>101</v>
       </c>
       <c r="N4" s="18" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="O4" s="18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P4" s="18" t="s">
         <v>45</v>
       </c>
       <c r="Q4" s="18" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="R4" s="18" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="S4" s="18" t="s">
         <v>6</v>
@@ -1423,7 +1423,7 @@
         <v>70</v>
       </c>
       <c r="X4" s="18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Y4" s="18" t="s">
         <v>120</v>
@@ -1450,7 +1450,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:35" s="6" customFormat="1" ht="81.599999999999994" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:35" s="6" customFormat="1" ht="73.5" x14ac:dyDescent="0.35">
       <c r="A6" s="16" t="s">
         <v>2</v>
       </c>
@@ -1492,7 +1492,7 @@
         <v>54</v>
       </c>
       <c r="O6" s="20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P6" s="5" t="s">
         <v>105</v>
@@ -1519,7 +1519,7 @@
         <v>13</v>
       </c>
       <c r="X6" s="20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Y6" s="5" t="s">
         <v>72</v>
@@ -1555,7 +1555,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="7" spans="1:35" s="5" customFormat="1" ht="61.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:35" s="5" customFormat="1" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
         <v>12</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:35" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:35" s="6" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="17" t="s">
         <v>3</v>
       </c>
@@ -1685,9 +1685,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:35" s="17" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:35" s="17" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:35" s="17" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:35" s="17" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="10" spans="1:35" s="17" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="1:35" s="17" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="17" t="s">
         <v>10</v>
       </c>

--- a/static/example_sheets/Field sampling (internal).xlsx
+++ b/static/example_sheets/Field sampling (internal).xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m\Documents\GitHub repoes\gg-metadatabase-ui\static\example_sheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\glj523\Documents\github repoes\upload_web_app\static\example_sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A048FC97-8BBA-4921-BA3B-9F99F29D3D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DAB1227-3708-4AEC-9CDB-45A8E1677EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F20BE04D-14A6-4DFA-9322-DA461E992517}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{F20BE04D-14A6-4DFA-9322-DA461E992517}"/>
   </bookViews>
   <sheets>
     <sheet name="eDNA_Archive_sampling_(20231027" sheetId="2" r:id="rId1"/>
@@ -46,9 +46,9 @@
   <commentList>
     <comment ref="O1" authorId="0" shapeId="0" xr:uid="{6FC7414E-1184-43F7-9F14-90F3FC65C183}">
       <text>
-        <t xml:space="preserve">[Trådet kommentar]
-Din version af Excel lader dig læse denne trådede kommentar. Eventuelle ændringer vil dog blive fjernet, hvis filen åbnes i en nyere version af Excel. Få mere at vide: https://go.microsoft.com/fwlink/?linkid=870924
-Kommentar:
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     URI: MIXS:0000018 </t>
       </text>
     </comment>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="125">
   <si>
     <t>Expected column names and positions:</t>
   </si>
@@ -292,9 +292,6 @@
     <t>Any relevant measurements/observations taken of the field sample. If multiple: seperate by semi-colon.</t>
   </si>
   <si>
-    <t>{measurement/observation type}: {measurement/observation} {unit (optional)}</t>
-  </si>
-  <si>
     <t>water content: 10 %; porosity: 5 %</t>
   </si>
   <si>
@@ -428,6 +425,23 @@
   </si>
   <si>
     <t>37.5</t>
+  </si>
+  <si>
+    <t>An id for the physical QR code on the sample</t>
+  </si>
+  <si>
+    <t>If relevant. Otherwise leave blank.</t>
+  </si>
+  <si>
+    <t>Eg. Glacial, Lacustrine
+Fluvial, Aeolian,Peat
+Soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Specify the storage setting </t>
+  </si>
+  <si>
+    <t>&lt;measurement/observation type&gt;: &lt;measurement/observation&gt; &lt;unit (optional)&gt;</t>
   </si>
 </sst>
 </file>
@@ -668,10 +682,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="8">
+    <cellStyle name="Check Cell" xfId="6" builtinId="23"/>
     <cellStyle name="Comma 2" xfId="3" xr:uid="{8942F21F-F0D4-468F-A2D9-2DD07A9F09D0}"/>
     <cellStyle name="Explanatory Text 2" xfId="2" xr:uid="{EEC8BC1F-FCCB-4C2D-96AE-E4673B111AFF}"/>
-    <cellStyle name="Kontrollér celle" xfId="6" builtinId="23"/>
-    <cellStyle name="Link" xfId="7" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="7" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{C43A14CE-CD9A-4CDB-8396-19B2B1DC1FD5}"/>
     <cellStyle name="Normal 4" xfId="4" xr:uid="{1133FEEC-7998-4312-B355-8FD805FAFB7D}"/>
@@ -697,9 +711,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022 Tema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -737,7 +751,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -843,7 +857,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -985,7 +999,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1008,61 +1022,61 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92B8DB45-AD95-4AEF-BE44-A884078F1D25}">
   <dimension ref="A1:AI11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.81640625" customWidth="1"/>
-    <col min="3" max="3" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.77734375" customWidth="1"/>
+    <col min="3" max="3" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="21.1796875" customWidth="1"/>
-    <col min="9" max="9" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.21875" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="8.90625" customWidth="1"/>
-    <col min="13" max="13" width="29.81640625" customWidth="1"/>
-    <col min="14" max="14" width="16.08984375" customWidth="1"/>
-    <col min="15" max="15" width="18.1796875" customWidth="1"/>
-    <col min="16" max="16" width="16.54296875" customWidth="1"/>
-    <col min="17" max="17" width="17.1796875" customWidth="1"/>
-    <col min="18" max="18" width="16.54296875" customWidth="1"/>
-    <col min="19" max="19" width="17.6328125" customWidth="1"/>
-    <col min="20" max="20" width="14.54296875" customWidth="1"/>
-    <col min="21" max="21" width="11.08984375" customWidth="1"/>
-    <col min="22" max="22" width="8.36328125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.54296875" customWidth="1"/>
-    <col min="25" max="25" width="18.1796875" customWidth="1"/>
-    <col min="26" max="26" width="21.36328125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="20.36328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.88671875" customWidth="1"/>
+    <col min="13" max="13" width="29.77734375" customWidth="1"/>
+    <col min="14" max="14" width="16.109375" customWidth="1"/>
+    <col min="15" max="15" width="18.21875" customWidth="1"/>
+    <col min="16" max="16" width="16.5546875" customWidth="1"/>
+    <col min="17" max="17" width="17.21875" customWidth="1"/>
+    <col min="18" max="18" width="16.5546875" customWidth="1"/>
+    <col min="19" max="19" width="17.6640625" customWidth="1"/>
+    <col min="20" max="20" width="14.5546875" customWidth="1"/>
+    <col min="21" max="21" width="11.109375" customWidth="1"/>
+    <col min="22" max="22" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.5546875" customWidth="1"/>
+    <col min="25" max="25" width="18.21875" customWidth="1"/>
+    <col min="26" max="26" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="20.33203125" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="25" customWidth="1"/>
-    <col min="29" max="29" width="12.6328125" customWidth="1"/>
-    <col min="30" max="30" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="31.54296875" customWidth="1"/>
-    <col min="32" max="32" width="43.6328125" customWidth="1"/>
-    <col min="33" max="33" width="13.08984375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="18.453125" customWidth="1"/>
-    <col min="36" max="36" width="56.453125" customWidth="1"/>
-    <col min="37" max="37" width="33.1796875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="48.08984375" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="26.6328125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="13.08984375" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="23.6328125" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.6640625" customWidth="1"/>
+    <col min="30" max="30" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="31.5546875" customWidth="1"/>
+    <col min="32" max="32" width="43.6640625" customWidth="1"/>
+    <col min="33" max="33" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="18.44140625" customWidth="1"/>
+    <col min="36" max="36" width="56.44140625" customWidth="1"/>
+    <col min="37" max="37" width="33.21875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="48.109375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="22" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="26.6328125" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="13.08984375" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="23.6328125" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="15.6328125" customWidth="1"/>
-    <col min="50" max="50" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="15.6640625" customWidth="1"/>
+    <col min="50" max="50" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" s="15" customFormat="1" ht="59" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:35" s="15" customFormat="1" ht="58.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -1073,22 +1087,22 @@
         <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>34</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>38</v>
@@ -1100,16 +1114,16 @@
         <v>16</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>37</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="Q1" s="3" t="s">
         <v>60</v>
@@ -1145,13 +1159,13 @@
         <v>42</v>
       </c>
       <c r="AB1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="AD1" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="AE1" s="1" t="s">
         <v>23</v>
@@ -1169,7 +1183,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:35" s="18" customFormat="1" ht="16" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:35" s="18" customFormat="1" ht="16.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
@@ -1177,13 +1191,13 @@
         <v>30</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G2" s="19">
         <v>61.139899999999997</v>
@@ -1192,7 +1206,7 @@
         <v>-45.534700000000001</v>
       </c>
       <c r="I2" s="18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J2" s="18" t="s">
         <v>65</v>
@@ -1204,13 +1218,13 @@
         <v>48</v>
       </c>
       <c r="M2" s="18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N2" s="18">
         <v>10</v>
       </c>
       <c r="O2" s="18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P2" s="18" t="s">
         <v>43</v>
@@ -1237,46 +1251,46 @@
         <v>5</v>
       </c>
       <c r="X2" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Y2" s="18">
         <v>37</v>
       </c>
       <c r="Z2" s="18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA2" s="18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB2" s="18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AC2" s="18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AD2" s="18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AE2" s="18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AF2" s="18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:35" s="18" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:35" s="18" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="18" t="s">
         <v>31</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G3" s="19">
         <v>61.139899999999997</v>
@@ -1285,7 +1299,7 @@
         <v>-45.534700000000001</v>
       </c>
       <c r="I3" s="18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J3" s="18" t="s">
         <v>65</v>
@@ -1297,13 +1311,13 @@
         <v>48</v>
       </c>
       <c r="M3" s="18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N3" s="18">
         <v>200</v>
       </c>
       <c r="O3" s="18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P3" s="18" t="s">
         <v>44</v>
@@ -1330,46 +1344,46 @@
         <v>5</v>
       </c>
       <c r="X3" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Y3" s="18">
         <v>37</v>
       </c>
       <c r="Z3" s="18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA3" s="18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AB3" s="18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AC3" s="18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AD3" s="18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AE3" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF3" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="AF3" s="18" t="s">
-        <v>81</v>
-      </c>
     </row>
-    <row r="4" spans="1:35" s="18" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:35" s="18" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="18" t="s">
         <v>32</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G4" s="19">
         <v>61.139899999999997</v>
@@ -1378,7 +1392,7 @@
         <v>-45.534700000000001</v>
       </c>
       <c r="I4" s="18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J4" s="18" t="s">
         <v>64</v>
@@ -1390,22 +1404,22 @@
         <v>48</v>
       </c>
       <c r="M4" s="18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="N4" s="18" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O4" s="18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P4" s="18" t="s">
         <v>45</v>
       </c>
       <c r="Q4" s="18" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="R4" s="18" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="S4" s="18" t="s">
         <v>6</v>
@@ -1423,34 +1437,34 @@
         <v>70</v>
       </c>
       <c r="X4" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Y4" s="18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z4" s="18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AA4" s="18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AB4" s="18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AC4" s="18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AD4" s="18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="AE4" s="18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AF4" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:35" s="6" customFormat="1" ht="73.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:35" s="6" customFormat="1" ht="81.599999999999994" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>2</v>
       </c>
@@ -1465,7 +1479,7 @@
         <v>62</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>7</v>
@@ -1474,7 +1488,7 @@
         <v>8</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>39</v>
@@ -1483,19 +1497,19 @@
         <v>66</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N6" s="5" t="s">
         <v>54</v>
       </c>
       <c r="O6" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q6" s="5" t="s">
         <v>54</v>
@@ -1507,63 +1521,71 @@
         <v>11</v>
       </c>
       <c r="T6" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="U6" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="V6" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="W6" s="5" t="s">
         <v>13</v>
       </c>
       <c r="X6" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Y6" s="5" t="s">
         <v>72</v>
       </c>
       <c r="Z6" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA6" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AB6" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AC6" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AD6" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AE6" s="5" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="AF6" s="5" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="AG6" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AH6" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AI6" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:35" s="5" customFormat="1" ht="52.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:35" s="5" customFormat="1" ht="61.2" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>120</v>
       </c>
       <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
+      <c r="E7" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>121</v>
+      </c>
       <c r="G7" s="9" t="s">
         <v>53</v>
       </c>
@@ -1571,7 +1593,7 @@
         <v>52</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>63</v>
@@ -1583,7 +1605,7 @@
         <v>68</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N7" s="12" t="s">
         <v>55</v>
@@ -1592,7 +1614,7 @@
         <v>56</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>58</v>
@@ -1603,6 +1625,9 @@
       <c r="S7" s="12" t="s">
         <v>59</v>
       </c>
+      <c r="T7" s="5" t="s">
+        <v>122</v>
+      </c>
       <c r="U7" s="5" t="s">
         <v>41</v>
       </c>
@@ -1613,31 +1638,34 @@
         <v>73</v>
       </c>
       <c r="Z7" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
+      </c>
+      <c r="AA7" s="5" t="s">
+        <v>123</v>
       </c>
       <c r="AB7" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AC7" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD7" s="5" t="s">
         <v>90</v>
-      </c>
-      <c r="AD7" s="5" t="s">
-        <v>91</v>
       </c>
       <c r="AE7" s="5" t="s">
         <v>74</v>
       </c>
       <c r="AF7" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AG7" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AH7" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="AH7" s="5" t="s">
-        <v>93</v>
-      </c>
     </row>
-    <row r="8" spans="1:35" s="6" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:35" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
         <v>3</v>
       </c>
@@ -1685,9 +1713,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:35" s="17" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="10" spans="1:35" s="17" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="1:35" s="17" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:35" s="17" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:35" s="17" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:35" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="s">
         <v>10</v>
       </c>
